--- a/analises/smartfit_kpis_1T26_estimate.xlsx
+++ b/analises/smartfit_kpis_1T26_estimate.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>+27 net adds vs 4T25 (1T tipicamente menor que 4T)</t>
+          <t>+27 net adds vs 4T25=693 (1T tipicamente menor que 4T)</t>
         </is>
       </c>
     </row>
@@ -553,11 +553,11 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1818</v>
+        <v>1770</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>+6% YoY (desaceleração; 1T25 foi +12% YoY vs 1T24)</t>
+          <t>+175 net adds vs 4T25=1595 (em linha com histórico 1T: +142/+172/+155)</t>
         </is>
       </c>
     </row>
@@ -568,11 +568,11 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>1T25 ex-TP foi 104.6; +0.4% YoY (repasse Black novos cancela vs 1T25)</t>
+          <t>Flat QoQ vs 4T25 normalizado (4T25=109.2 inflado por aberturas; +2.3% YoY vs 1T25=104.6)</t>
         </is>
       </c>
     </row>
@@ -593,11 +593,11 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.165</v>
+        <v>0.175</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Default: 2026 anual 18% × peso MAU 1T26 × intensidade 1.10 = 16.5%</t>
+          <t>Default: 2026 anual 19% (extrapolação 11→15→19) × peso MAU 1T26 × intensidade 1.10 = 17.5%</t>
         </is>
       </c>
     </row>
@@ -608,11 +608,11 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.138</v>
+        <v>0.14</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Default: 2026 anual 15% × mesmo peso = 13.8%</t>
+          <t>Default: 2026 anual 15.5% × mesmo peso = 14.0% (ratio rev/freq ~0.8)</t>
         </is>
       </c>
     </row>
